--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:30:44+00:00</t>
+          <t>2026-09-14T00:33:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:33:16+00:00</t>
+          <t>2026-09-15T01:05:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:05:06+00:00</t>
+          <t>2026-09-16T00:54:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:54:54+00:00</t>
+          <t>2026-09-17T02:23:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:23:20+00:00</t>
+          <t>2026-09-18T00:54:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$B$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:54:36+00:00</t>
+          <t>2026-09-19T00:49:15+00:00</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -783,293 +783,281 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Ethiopia-Related Sanctions</t>
+          <t>Foreign Interference in a United States Election Sanctions</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/ethiopia</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/foreign-interference-in-a-united-states-election-sanctions</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Foreign Interference in a United States Election Sanctions</t>
+          <t>Global Magnitsky Sanctions</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/foreign-interference-in-a-united-states-election-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/global-magnitsky-sanctions</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Global Magnitsky Sanctions</t>
+          <t>Hong Kong-Related Sanctions</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/global-magnitsky-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hong-kong-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong-Related Sanctions</t>
+          <t>Hostages and Wrongfully Detained U.S. Nationals Sanctions</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hong-kong-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hostages-and-wrongfully-detained-us-nationals-sanctions</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Hostages and Wrongfully Detained U.S. Nationals Sanctions</t>
+          <t>International Criminal Court-Related Sanctions</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hostages-and-wrongfully-detained-us-nationals-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/international-criminal-court-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>International Criminal Court-Related Sanctions</t>
+          <t>Iraq-Related Sanctions</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/international-criminal-court-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/iraq-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Iraq-Related Sanctions</t>
+          <t>Lebanon-Related Sanctions</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/iraq-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/lebanon-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Lebanon-Related Sanctions</t>
+          <t>Libya Sanctions</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/lebanon-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/libya-sanctions</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Libya Sanctions</t>
+          <t>Magnitsky Sanctions</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/libya-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/the-magnitsky-sanctions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Magnitsky Sanctions</t>
+          <t>Mali-Related Sanctions</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/the-magnitsky-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/mali-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Mali-Related Sanctions</t>
+          <t>Nicaragua-related Sanctions</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/mali-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/nicaragua-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Nicaragua-related Sanctions</t>
+          <t>Non-Proliferation Sanctions</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/nicaragua-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/non-proliferation-sanctions</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Non-Proliferation Sanctions</t>
+          <t>Promoting Accountability for Assad and Regional Stabilization Sanctions (PAARSS)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/non-proliferation-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/paarss</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Promoting Accountability for Assad and Regional Stabilization Sanctions (PAARSS)</t>
+          <t>Rough Diamond Trade Controls</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/paarss</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/rough-diamond-trade-controls</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Rough Diamond Trade Controls</t>
+          <t>Russian Harmful Foreign Activities Sanctions</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/rough-diamond-trade-controls</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/russian-harmful-foreign-activities-sanctions</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Russian Harmful Foreign Activities Sanctions</t>
+          <t>Somalia Sanctions</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/russian-harmful-foreign-activities-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/somalia-sanctions</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Somalia Sanctions</t>
+          <t>South Sudan-Related Sanctions</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/somalia-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/south-sudan-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>South Sudan-Related Sanctions</t>
+          <t>Sudan and Darfur Sanctions</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/south-sudan-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sudan-and-darfur-sanctions</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Sudan and Darfur Sanctions</t>
+          <t>Transnational Criminal Organizations</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sudan-and-darfur-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/transnational-criminal-organizations</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Transnational Criminal Organizations</t>
+          <t>Ukraine-/Russia-related Sanctions</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/transnational-criminal-organizations</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/ukraine-russia-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Ukraine-/Russia-related Sanctions</t>
+          <t>Venezuela-Related Sanctions</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/ukraine-russia-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/venezuela-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Venezuela-Related Sanctions</t>
+          <t>Yemen-related Sanctions</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/venezuela-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/yemen-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Yemen-related Sanctions</t>
+          <t>List of Country-related Sanctions</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/yemen-related-sanctions</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>List of Country-related Sanctions</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
           <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/where-is-ofacs-country-list-what-countries-do-i-need-to-worry-about-in-terms-of-us-sanctions</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B44"/>
+  <autoFilter ref="A1:B43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T00:49:15+00:00</t>
+          <t>2026-09-20T00:31:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:31:26+00:00</t>
+          <t>2026-09-21T00:41:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21T00:41:28+00:00</t>
+          <t>2026-09-22T01:23:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:23:40+00:00</t>
+          <t>2026-09-23T01:04:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:04:38+00:00</t>
+          <t>2026-09-24T00:59:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T00:59:27+00:00</t>
+          <t>2026-09-25T01:02:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:02:36+00:00</t>
+          <t>2026-09-26T01:05:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:05:24+00:00</t>
+          <t>2026-09-27T01:02:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:02:53+00:00</t>
+          <t>2026-09-28T01:21:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:21:40+00:00</t>
+          <t>2026-09-29T02:26:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:26:43+00:00</t>
+          <t>2026-09-30T01:45:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:45:59+00:00</t>
+          <t>2026-10-01T01:44:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:44:17+00:00</t>
+          <t>2026-10-02T01:54:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:54:35+00:00</t>
+          <t>2026-10-03T01:37:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:37:25+00:00</t>
+          <t>2026-10-04T02:17:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:17:49+00:00</t>
+          <t>2026-10-05T01:26:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:26:26+00:00</t>
+          <t>2026-10-06T02:37:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06T02:37:07+00:00</t>
+          <t>2026-10-07T01:55:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:55:28+00:00</t>
+          <t>2026-10-08T02:23:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:23:36+00:00</t>
+          <t>2026-10-09T02:41:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:41:00+00:00</t>
+          <t>2026-10-10T02:01:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:01:12+00:00</t>
+          <t>2026-10-10T09:15:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:15:53+00:00</t>
+          <t>2026-10-10T16:03:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:03:48+00:00</t>
+          <t>2026-10-10T22:08:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:08:12+00:00</t>
+          <t>2026-10-11T01:26:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:26:19+00:00</t>
+          <t>2026-10-11T09:32:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:32:55+00:00</t>
+          <t>2026-10-11T16:29:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:29:16+00:00</t>
+          <t>2026-10-11T22:36:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:36:53+00:00</t>
+          <t>2026-10-12T01:56:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:56:36+00:00</t>
+          <t>2026-10-12T10:02:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:02:58+00:00</t>
+          <t>2026-10-12T20:05:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:05:03+00:00</t>
+          <t>2026-10-13T03:18:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:18:18+00:00</t>
+          <t>2026-10-13T14:43:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:43:33+00:00</t>
+          <t>2026-10-13T20:28:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:28:27+00:00</t>
+          <t>2026-10-14T01:30:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:45+00:00</t>
+          <t>2026-10-14T08:15:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:15:38+00:00</t>
+          <t>2026-10-14T15:40:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:40:04+00:00</t>
+          <t>2026-10-14T22:00:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:00:14+00:00</t>
+          <t>2026-10-15T01:08:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:08:28+00:00</t>
+          <t>2026-10-15T07:53:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:53:14+00:00</t>
+          <t>2026-10-15T15:26:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:26:10+00:00</t>
+          <t>2026-10-15T21:54:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:54:01+00:00</t>
+          <t>2026-10-16T00:55:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:55:56+00:00</t>
+          <t>2026-10-16T07:45:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:45:02+00:00</t>
+          <t>2026-10-16T15:06:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:06:01+00:00</t>
+          <t>2026-10-16T21:52:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:52:01+00:00</t>
+          <t>2026-10-17T00:56:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:56:11+00:00</t>
+          <t>2026-10-17T07:22:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:22:19+00:00</t>
+          <t>2026-10-17T14:00:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:00:51+00:00</t>
+          <t>2026-10-17T17:40:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:40:37+00:00</t>
+          <t>2026-10-17T21:10:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:10:42+00:00</t>
+          <t>2026-10-18T00:31:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:31:30+00:00</t>
+          <t>2026-10-18T07:36:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:30+00:00</t>
+          <t>2026-10-18T14:14:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:14:18+00:00</t>
+          <t>2026-10-18T17:42:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:42:40+00:00</t>
+          <t>2026-10-18T21:12:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:12:45+00:00</t>
+          <t>2026-10-19T00:38:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:38:08+00:00</t>
+          <t>2026-10-19T08:19:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:19:26+00:00</t>
+          <t>2026-10-19T17:17:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:17:35+00:00</t>
+          <t>2026-10-19T22:42:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:42:58+00:00</t>
+          <t>2026-10-20T01:23:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:23:15+00:00</t>
+          <t>2026-10-20T08:04:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:04:14+00:00</t>
+          <t>2026-10-20T15:30:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:30:36+00:00</t>
+          <t>2026-10-20T22:01:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:01:00+00:00</t>
+          <t>2026-10-21T01:10:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:10:02+00:00</t>
+          <t>2026-10-21T08:09:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:09:41+00:00</t>
+          <t>2026-10-21T15:46:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:46:43+00:00</t>
+          <t>2026-10-21T22:03:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:03:34+00:00</t>
+          <t>2026-10-22T01:06:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:06:48+00:00</t>
+          <t>2026-10-22T08:09:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:09:47+00:00</t>
+          <t>2026-10-22T15:45:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:45:45+00:00</t>
+          <t>2026-10-22T22:00:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:00:59+00:00</t>
+          <t>2026-10-23T01:07:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:07:48+00:00</t>
+          <t>2026-10-23T08:08:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:08:27+00:00</t>
+          <t>2026-10-23T15:33:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:33:54+00:00</t>
+          <t>2026-10-23T21:47:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:47:47+00:00</t>
+          <t>2026-10-24T01:16:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:16:53+00:00</t>
+          <t>2026-10-24T07:47:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:47:09+00:00</t>
+          <t>2026-10-24T09:09:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:09:36+00:00</t>
+          <t>2026-10-24T14:12:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:02+00:00</t>
+          <t>2026-10-24T15:22:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:22:41+00:00</t>
+          <t>2026-10-24T17:44:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:18+00:00</t>
+          <t>2026-10-24T21:20:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:20:37+00:00</t>
+          <t>2026-10-25T00:42:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:42:28+00:00</t>
+          <t>2026-10-25T07:57:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:57:15+00:00</t>
+          <t>2026-10-25T14:42:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:42:44+00:00</t>
+          <t>2026-10-25T18:00:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:00:25+00:00</t>
+          <t>2026-10-25T21:25:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:25:26+00:00</t>
+          <t>2026-10-26T00:56:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:56:48+00:00</t>
+          <t>2026-10-26T08:28:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$B$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$B$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:28:28+00:00</t>
+          <t>2026-10-26T17:04:48+00:00</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -639,425 +639,401 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Where is OFAC's country list?​</t>
+          <t>Afghanistan-Related Sanctions</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/where-is-ofacs-country-list-what-countries-do-i-need-to-worry-about-in-terms-of-us-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/afghanistan-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Afghanistan-Related Sanctions</t>
+          <t>Balkans-Related Sanctions</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/afghanistan-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/balkans-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Balkans-Related Sanctions</t>
+          <t>Belarus Sanctions</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/balkans-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/belarus-sanctions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Belarus Sanctions</t>
+          <t>Burma-Related Sanctions</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/belarus-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/burma</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Burma-Related Sanctions</t>
+          <t>Central African Republic Sanctions</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/burma</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/central-african-republic-sanctions</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Central African Republic Sanctions</t>
+          <t>Chinese Military Companies Sanctions</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/central-african-republic-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/chinese-military-companies-sanctions</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Chinese Military Companies Sanctions</t>
+          <t>Counter Narcotics Trafficking Sanctions</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/chinese-military-companies-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/counter-narcotics-trafficking-sanctions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Counter Narcotics Trafficking Sanctions</t>
+          <t>Counter Terrorism Sanctions</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/counter-narcotics-trafficking-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/counter-terrorism-sanctions</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Counter Terrorism Sanctions</t>
+          <t>Countering America's Adversaries Through Sanctions Act-Related Sanctions</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/counter-terrorism-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/countering-americas-adversaries-through-sanctions-act-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Countering America's Adversaries Through Sanctions Act-Related Sanctions</t>
+          <t>Cyber-Related Sanctions</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/countering-americas-adversaries-through-sanctions-act-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sanctions-related-to-significant-malicious-cyber-enabled-activities</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Cyber-Related Sanctions</t>
+          <t>Democratic Republic of the Congo-Related Sanctions</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sanctions-related-to-significant-malicious-cyber-enabled-activities</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/democratic-republic-of-the-congo-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo-Related Sanctions</t>
+          <t>Foreign Interference in a United States Election Sanctions</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/democratic-republic-of-the-congo-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/foreign-interference-in-a-united-states-election-sanctions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Foreign Interference in a United States Election Sanctions</t>
+          <t>Global Magnitsky Sanctions</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/foreign-interference-in-a-united-states-election-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/global-magnitsky-sanctions</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Global Magnitsky Sanctions</t>
+          <t>Hong Kong-Related Sanctions</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/global-magnitsky-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hong-kong-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong-Related Sanctions</t>
+          <t>Hostages and Wrongfully Detained U.S. Nationals Sanctions</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hong-kong-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hostages-and-wrongfully-detained-us-nationals-sanctions</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Hostages and Wrongfully Detained U.S. Nationals Sanctions</t>
+          <t>International Criminal Court-Related Sanctions</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/hostages-and-wrongfully-detained-us-nationals-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/international-criminal-court-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>International Criminal Court-Related Sanctions</t>
+          <t>Iraq-Related Sanctions</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/international-criminal-court-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/iraq-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Iraq-Related Sanctions</t>
+          <t>Lebanon-Related Sanctions</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/iraq-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/lebanon-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Lebanon-Related Sanctions</t>
+          <t>Libya Sanctions</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/lebanon-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/libya-sanctions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Libya Sanctions</t>
+          <t>Magnitsky Sanctions</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/libya-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/the-magnitsky-sanctions</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Magnitsky Sanctions</t>
+          <t>Mali-Related Sanctions</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/the-magnitsky-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/mali-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Mali-Related Sanctions</t>
+          <t>Nicaragua-related Sanctions</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/mali-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/nicaragua-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Nicaragua-related Sanctions</t>
+          <t>Non-Proliferation Sanctions</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/nicaragua-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/non-proliferation-sanctions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Non-Proliferation Sanctions</t>
+          <t>Promoting Accountability for Assad and Regional Stabilization Sanctions (PAARSS)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/non-proliferation-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/paarss</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Promoting Accountability for Assad and Regional Stabilization Sanctions (PAARSS)</t>
+          <t>Rough Diamond Trade Controls</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/paarss</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/rough-diamond-trade-controls</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Rough Diamond Trade Controls</t>
+          <t>Russian Harmful Foreign Activities Sanctions</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/rough-diamond-trade-controls</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/russian-harmful-foreign-activities-sanctions</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Russian Harmful Foreign Activities Sanctions</t>
+          <t>Somalia Sanctions</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/russian-harmful-foreign-activities-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/somalia-sanctions</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Somalia Sanctions</t>
+          <t>South Sudan-Related Sanctions</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/somalia-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/south-sudan-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>South Sudan-Related Sanctions</t>
+          <t>Sudan and Darfur Sanctions</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/south-sudan-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sudan-and-darfur-sanctions</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Sudan and Darfur Sanctions</t>
+          <t>Transnational Criminal Organizations</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/sudan-and-darfur-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/transnational-criminal-organizations</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Transnational Criminal Organizations</t>
+          <t>Ukraine-/Russia-related Sanctions</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/transnational-criminal-organizations</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/ukraine-russia-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ukraine-/Russia-related Sanctions</t>
+          <t>Venezuela-Related Sanctions</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/ukraine-russia-related-sanctions</t>
+          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/venezuela-related-sanctions</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Venezuela-Related Sanctions</t>
+          <t>Yemen-related Sanctions</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/venezuela-related-sanctions</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Yemen-related Sanctions</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
           <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/yemen-related-sanctions</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>List of Country-related Sanctions</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>https://ofac.treasury.gov/sanctions-programs-and-country-information/where-is-ofacs-country-list-what-countries-do-i-need-to-worry-about-in-terms-of-us-sanctions</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B43"/>
+  <autoFilter ref="A1:B41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:04:48+00:00</t>
+          <t>2026-10-26T22:57:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:57:06+00:00</t>
+          <t>2026-10-27T01:44:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:44:38+00:00</t>
+          <t>2026-10-27T01:47:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:47:48+00:00</t>
+          <t>2026-10-27T08:31:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:31:42+00:00</t>
+          <t>2026-10-27T16:08:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:03+00:00</t>
+          <t>2026-10-27T22:46:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:46:36+00:00</t>
+          <t>2026-10-28T01:56:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:03+00:00</t>
+          <t>2026-10-28T09:09:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:09:50+00:00</t>
+          <t>2026-10-28T16:55:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:55:25+00:00</t>
+          <t>2026-10-28T22:55:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:55:28+00:00</t>
+          <t>2026-10-29T02:00:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:00:36+00:00</t>
+          <t>2026-10-29T06:40:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:40:56+00:00</t>
+          <t>2026-10-29T09:09:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:15+00:00</t>
+          <t>2026-10-29T17:13:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:10+00:00</t>
+          <t>2026-10-29T23:03:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:03:35+00:00</t>
+          <t>2026-10-30T02:16:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:16:53+00:00</t>
+          <t>2026-10-30T09:20:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:07+00:00</t>
+          <t>2026-10-30T16:54:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:54:11+00:00</t>
+          <t>2026-10-30T22:44:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ofac-country-programs.xlsx
+++ b/public/downloads/ofac-country-programs.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:44:40+00:00</t>
+          <t>2026-10-31T01:56:06+00:00</t>
         </is>
       </c>
     </row>
